--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://owogemeenten-my.sharepoint.com/personal/a_celem_owo-gemeenten_nl/Documents/Bureaublad/VsCode/SQL_gen_NL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_56F306114DB3BDA22DFB8FA993BBC61CCF8836E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D74FEDDD-7C6B-4F69-B5CA-3C8040B37F41}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_56F306114DB3BDA22DFB8FA993BBC61CCF8836E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D1C5ABB-C99A-46F0-A32C-6527EFBED815}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="1230" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="49">
   <si>
     <t>source_system</t>
   </si>
@@ -153,12 +153,6 @@
   </si>
   <si>
     <t>DIM_PW_RedenInstroom</t>
-  </si>
-  <si>
-    <t>LEFT</t>
-  </si>
-  <si>
-    <t>[VW_GGM_Inkomensvoorziening].[PersoonID] = [VW_GGM_Persoon].[PersoonID]</t>
   </si>
   <si>
     <t>DIM_PW_RedenUitstroom</t>
@@ -226,6 +220,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -766,7 +764,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -790,7 +788,7 @@
         <v>19</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -801,7 +799,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -825,7 +823,7 @@
         <v>25</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -836,7 +834,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -860,7 +858,7 @@
         <v>30</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -871,7 +869,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -895,7 +893,7 @@
         <v>30</v>
       </c>
       <c r="O10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -906,7 +904,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
@@ -930,7 +928,7 @@
         <v>19</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -941,7 +939,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -965,7 +963,7 @@
         <v>19</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -976,7 +974,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -1000,7 +998,7 @@
         <v>25</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1011,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
@@ -1035,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -1046,7 +1044,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -1070,7 +1068,7 @@
         <v>30</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1081,7 +1079,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
@@ -1105,7 +1103,7 @@
         <v>19</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -1140,7 +1138,7 @@
         <v>19</v>
       </c>
       <c r="O17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -1175,7 +1173,7 @@
         <v>25</v>
       </c>
       <c r="O18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -1210,7 +1208,7 @@
         <v>30</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -1245,7 +1243,7 @@
         <v>30</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -1280,7 +1278,7 @@
         <v>19</v>
       </c>
       <c r="O21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -1291,7 +1289,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
         <v>37</v>
@@ -1326,7 +1324,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -1361,7 +1359,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
@@ -1396,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
@@ -1431,7 +1429,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
         <v>34</v>
@@ -1466,7 +1464,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
         <v>37</v>
@@ -1490,7 +1488,7 @@
         <v>19</v>
       </c>
       <c r="O27">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -1501,7 +1499,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -1525,7 +1523,7 @@
         <v>25</v>
       </c>
       <c r="O28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -1536,7 +1534,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
@@ -1560,7 +1558,7 @@
         <v>30</v>
       </c>
       <c r="O29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -1571,7 +1569,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -1595,7 +1593,7 @@
         <v>30</v>
       </c>
       <c r="O30">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -1606,7 +1604,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D31" t="s">
         <v>34</v>
@@ -1630,7 +1628,7 @@
         <v>19</v>
       </c>
       <c r="O31">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1849,12 +1847,6 @@
       <c r="J6" t="s">
         <v>19</v>
       </c>
-      <c r="M6" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1879,7 +1871,7 @@
         <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I7" t="s">
         <v>39</v>
@@ -1911,7 +1903,7 @@
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1943,7 +1935,7 @@
         <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
         <v>29</v>
@@ -1975,7 +1967,7 @@
         <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I10" t="s">
         <v>33</v>
@@ -2007,7 +1999,7 @@
         <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I11" t="s">
         <v>35</v>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://owogemeenten-my.sharepoint.com/personal/a_celem_owo-gemeenten_nl/Documents/Bureaublad/VsCode/SQL_gen_NL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_56F306114DB3BDA22DFB8FA993BBC61CCF8836E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D1C5ABB-C99A-46F0-A32C-6527EFBED815}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_56F306114DB3BDA22DFB8FA993BBC61CCF8836E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FD8FBC3-3C5D-4604-83C4-49DA1A41DC14}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="1230" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Silver_to_GGM" sheetId="1" r:id="rId1"/>
@@ -1487,9 +1487,6 @@
       <c r="J27" t="s">
         <v>19</v>
       </c>
-      <c r="O27">
-        <v>3</v>
-      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1522,9 +1519,6 @@
       <c r="J28" t="s">
         <v>25</v>
       </c>
-      <c r="O28">
-        <v>3</v>
-      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1557,9 +1551,6 @@
       <c r="J29" t="s">
         <v>30</v>
       </c>
-      <c r="O29">
-        <v>3</v>
-      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1592,9 +1583,6 @@
       <c r="J30" t="s">
         <v>30</v>
       </c>
-      <c r="O30">
-        <v>3</v>
-      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1626,9 +1614,6 @@
       </c>
       <c r="J31" t="s">
         <v>19</v>
-      </c>
-      <c r="O31">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://owogemeenten-my.sharepoint.com/personal/a_celem_owo-gemeenten_nl/Documents/Bureaublad/VsCode/SQL_gen_NL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_56F306114DB3BDA22DFB8FA993BBC61CCF8836E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FD8FBC3-3C5D-4604-83C4-49DA1A41DC14}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_56F306114DB3BDA22DFB8FA993BBC61CCF8836E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC99ACF6-8FD6-43A0-A46A-0CFF65D93452}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1487,6 +1487,9 @@
       <c r="J27" t="s">
         <v>19</v>
       </c>
+      <c r="O27">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1519,6 +1522,9 @@
       <c r="J28" t="s">
         <v>25</v>
       </c>
+      <c r="O28">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1551,6 +1557,9 @@
       <c r="J29" t="s">
         <v>30</v>
       </c>
+      <c r="O29">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1583,6 +1592,9 @@
       <c r="J30" t="s">
         <v>30</v>
       </c>
+      <c r="O30">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1614,6 +1626,9 @@
       </c>
       <c r="J31" t="s">
         <v>19</v>
+      </c>
+      <c r="O31">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
